--- a/OUT_EXCEL/out_6.xlsx
+++ b/OUT_EXCEL/out_6.xlsx
@@ -454,12 +454,12 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nam 2023</t>
+          <t>Năm 2023</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nam2022</t>
+          <t>Năm 2022</t>
         </is>
       </c>
     </row>
@@ -469,17 +469,13 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CHI TIEU</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
+          <t>CHỈ TIÊU</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>MS   TM</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -499,7 +495,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Luru chuyen tien tir hoat dong kinh doanh</t>
+          <t>L   Lưu chuyển tiền từ hoạt động kinh doanh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -513,7 +509,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>I. Lgi nhugn truoc thue</t>
+          <t>1.  Lợi nhuận trước thuế</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -539,7 +535,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2. Dieu chinh cho cac khoan</t>
+          <t>2.  Điều chinh cho các khoản</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -553,7 +549,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-Khau hao tai san co dinh va BDS dau tur</t>
+          <t>-Khấu hao tài sản cố định và BĐS đầu tu</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -579,7 +575,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-Lai, lo chenh lech ty gia hoi doai chua thuc hien</t>
+          <t>-Lãi, lỗ chênh lệch tỷ giá hối đoái chua thực hiện</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -605,7 +601,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-Lai, lo tir hoat dong dau tu</t>
+          <t>-Lãi, lỗ từ hoạt động đầu tu</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -616,7 +612,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>291.422.412)</t>
+          <t>(291.422.412)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -631,7 +627,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-Chi phi lai vay</t>
+          <t>-Chi phí lãi vay</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -657,7 +653,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Loi nhuan tir hoat dong kinh doanh truoc</t>
+          <t>Lợi nhuận từ hoat động kinh doanh trước</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -697,7 +693,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>thay doi von luu dong</t>
+          <t>thay đỗi vốn Iưu động</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -711,7 +707,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-Tang,giam cac khoan phai thu</t>
+          <t>-Tăng, giảm các khoàn phải thu</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -727,7 +723,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6.784.490.904)</t>
+          <t>(6.784.490.904)</t>
         </is>
       </c>
     </row>
@@ -737,7 +733,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-Tang,giam hang ton kho</t>
+          <t>-Tăng, giảm hàng tồn kho</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -748,7 +744,7 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>9.672.956.641)</t>
+          <t>(9.672.956.641)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -763,7 +759,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-Tanggiam cac khoan phai tra</t>
+          <t>-Tăng, giảm các khoản phải trả</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -789,7 +785,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-Tang.giam chi phi tra truoc</t>
+          <t>- Tăng, giảm chi phí trả truớc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -815,7 +811,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-Tien lai vay da tra</t>
+          <t>- Tiền lãi vav đã trả</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -831,7 +827,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.225.905.429)</t>
+          <t>(1.225.905.429)</t>
         </is>
       </c>
     </row>
@@ -841,7 +837,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Luu chuyen tien thuan tir hogt dong kinh doanh</t>
+          <t>Luu chuyển tiền thuần từ hoat động kinh doanh</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -867,7 +863,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>II. Luu chuyen tien tur hoat dong dau tu</t>
+          <t>IL Lưu chuyến tiền từ hoạt động đầu tư</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -881,7 +877,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tien chi de mua sam,xay dung TSCD</t>
+          <t>Tiền chi để mua sắm, xây dựng TSCĐ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -921,7 +917,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>va cac tai san dai han khac</t>
+          <t>và các tài sản dài hạn khác</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -935,7 +931,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tien thu tur thanh ly,nhuong ban TSCD</t>
+          <t>Tiền thu từ thanh lý, nhuợng bán TSCĐ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -949,7 +945,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -975,7 +971,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>va cac tai san dai han khac</t>
+          <t>và các tài sản dài hạn khác</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -989,7 +985,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7. Tien thu lai cho vay,co turc va lgi nhuan dugc chia</t>
+          <t>7. Tiền thu lãi cho vay; cổ tức và lợi nhuận được chia</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1015,7 +1011,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Luu chuyen tien thuan tir hogt dong dau tu</t>
+          <t>Lưu chuyễn tiền thuần từ hoạt động đầu tư</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1041,7 +1037,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>III. Luru chuyen tien tir hoat dong tai chinh</t>
+          <t>IIL.   Lưu chuyển tiền từ hoạt động tài chính</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -1055,7 +1051,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3. Tien thu tir di vay</t>
+          <t>3.  Tiền thu từ đi vay</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1081,7 +1077,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4. Tien tra no goc vay</t>
+          <t>4.   Tiền trả nợ gốc vay</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1090,11 +1086,7 @@
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>(56.208.384.521)(71.828.683.426)</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1103,7 +1095,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Luu chuyen tien thuan tir hogt dong tii chinh</t>
+          <t>Lưu chuyển tiền thuần từ hoạt động tài chính</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1129,7 +1121,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Luru chuyen tien thuan trong ky 50=20+30+40)</t>
+          <t>Lưu chuyển tiền thuần trong kỳ (50 = 20+30+40)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1155,7 +1147,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tien va tuong durong tien dau ky</t>
+          <t>Tiền và tương đương tiền đầu kỳ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1181,7 +1173,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Anh huong cua thay doi ty gia hoi doai quy doingoai te</t>
+          <t>Ảnh hưởng của thay dổi tỷ giá hối đoái quy đổingoại tệ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1197,7 +1189,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>13.127)</t>
+          <t>(13.127)</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1199,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tien va turong durong tien cuoi ky 70=50+60+61)</t>
+          <t>Tiền và tương đương tiền cuối kỳ (70 = 50+60+61)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
